--- a/exercisesLifeContingencies/test2_2021_22/makeham.xlsx
+++ b/exercisesLifeContingencies/test2_2021_22/makeham.xlsx
@@ -1,37 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="makeham" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="makeham" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>lx</t>
+  </si>
+  <si>
+    <t>dx</t>
+  </si>
+  <si>
+    <t>qx</t>
+  </si>
+  <si>
+    <t>px</t>
+  </si>
+  <si>
+    <t>exo</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +72,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,2567 +388,2551 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F127"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>lx</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dx</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>qx</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>exo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>100000</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>30.09990444425847</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.0003009990444425847</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.9996990009555574</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>117.5179031967229</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>99969.90009555574</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>30.10023792762853</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.0003010930079839769</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.999698906992016</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>116.5531360788316</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:6">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>99939.79985762811</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>30.10141081574212</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.0003011954282340357</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.999698804571766</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>115.5880893908574</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:6">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>99909.69844681237</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>30.10349813338812</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.0003013070662946093</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.9996986929337054</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>114.622763841012</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:6">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>99879.59494867898</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>30.10658163232696</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.0003014287517665304</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.9996985712482335</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>113.6571602000485</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:6">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>99849.48836704665</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>30.11075039430957</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.0003015613889139068</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.9996984386110861</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>112.6912793060805</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:6">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>99819.37761665235</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>30.11610148828679</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.0003017059633846353</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.9996982940366154</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>111.7251220697629</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:6">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>99789.26151516406</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>30.12274068633165</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.0003018635495338762</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.9996981364504661</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>110.7586894798574</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:6">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>99759.13877447773</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>30.13078324387944</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.0003020353184082225</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.9996979646815918</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>109.7919826092129</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:6">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>99729.00799123386</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>30.14035474980654</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.000302222546447628</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.9996977774535524</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>108.8250026211896</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:6">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>99698.86763648405</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>30.15159205270328</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.0003024266249707086</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.9996975733750293</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>107.8577507765566</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:6">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>99668.71604443135</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>30.16464427010727</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.0003026490705133611</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.9996973509294866</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>106.8902284408988</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:6">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>99638.55140016125</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>30.17967388821574</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.0003028915360984152</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.9996971084639016</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>105.9224370925666</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:6">
+      <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>99608.37172627304</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>30.1968579600901</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>0.0003031558235192522</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.9996968441764807</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>104.9543783312076</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:6">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>99578.17486831294</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>30.21638941113465</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.0003034438967283171</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.9996965561032717</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>103.98605388692</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:6">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>99547.95847890181</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>30.23847846161812</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>0.0003037578964316667</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.9996962421035683</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>103.0174656300702</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:6">
+      <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>99517.7200004402</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>30.26335417650242</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.0003041001559960232</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.999695899844004</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>102.0486155818213</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:6">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>99487.4566462637</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>30.29126615408787</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>0.000304473218787682</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.9996955267812123</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>101.0795059254193</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:6">
+      <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>99457.16538010961</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>30.32248636586902</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>0.0003048798570719491</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.9996951201429281</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>100.1101390182888</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:6">
+      <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>99426.84289374374</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>30.35731116109752</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>0.0003053230926133299</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.9996946769073867</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>99.14051740499384</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:6">
+      <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>99396.48558258264</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>30.39606345078719</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>0.0003058062191296784</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.9996941937808703</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>98.17064383111851</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:6">
+      <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>99366.08951913186</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>30.43909508714066</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.0003063328267666199</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.9996936671732334</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>97.20052125813147</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:6">
+      <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>99335.65042404471</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>30.4867894559334</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.0003069068287748777</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.9996930931712251</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>96.23015287929654</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:6">
+      <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>99305.16363458878</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>30.53956430083946</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.000307532490588458</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.9996924675094115</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>95.25954213669864</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:6">
+      <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>99274.62407028794</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>30.59787480034333</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>0.0003082144615191851</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>0.9996917855384808</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>94.28869273945642</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:6">
+      <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>99244.0261954876</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>30.66221691986225</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>0.0003089578093039558</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>0.999691042190696</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>93.31760868319773</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:6">
+      <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>99213.36397856774</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>30.733131063428</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>0.0003097680577595074</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>0.9996902319422405</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>92.34629427087766</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:6">
+      <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>99182.6308475043</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>30.81120605201341</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>0.0003106512278282514</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>0.9996893487721717</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>91.37475413502322</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:6">
+      <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>99151.8196414523</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>30.8970834569968</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>0.0003116138823142656</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>0.9996883861176857</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>90.40299326149317</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:6">
+      <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>99120.92255799531</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>30.99146232103877</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>0.0003126631746481756</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>0.9996873368253518</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>89.43101701484561</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:6">
+      <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>99089.93109567427</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>31.09510430026764</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>0.0003138069020377499</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>0.9996861930979623</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>88.45883116541077</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:6">
+      <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>99058.835991374</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>31.2088392655148</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>0.0003150535634017793</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>0.9996849464365982</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>87.48644191817047</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:6">
+      <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>99027.62715210849</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>31.33357140339779</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>0.0003164124225178977</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>0.9996835875774821</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>86.51385594355079</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:6">
+      <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>98996.29358070508</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>31.47028586130405</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>0.0003178935768504143</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>0.9996821064231496</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>85.54108041023946</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:6">
+      <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>98964.82329484378</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>31.62005598489995</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>0.0003195080325733013</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>0.9996804919674267</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>84.56812302014228</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:6">
+      <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>98933.20323885889</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>31.78405120020602</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>0.0003212677863413393</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>0.9996787322136587</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>83.59499204560002</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:6">
+      <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>98901.41918765868</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>31.96354559760349</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>0.0003231859144200433</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>0.99967681408558</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>82.62169636898942</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:6">
+      <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>98869.45564206108</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>32.15992727951229</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>0.0003252766698336185</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>0.9996747233301664</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>81.64824552483736</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:6">
+      <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>98837.29571478156</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>32.37470853926046</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>0.0003275555882537029</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>0.9996724444117463</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>80.6746497445812</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:6">
+      <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>98804.92100624231</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>32.60953694427821</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>0.0003300396034142672</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>0.9996699603965857</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>79.70092000411164</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:6">
+      <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>98772.31146929803</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>32.86620740305097</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>0.0003327471729085429</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>0.9996672528270915</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>78.72706807423855</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:6">
+      <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>98739.44526189497</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>33.14667530243699</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>0.0003356984153042308</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>0.9996643015846958</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>77.75310657422241</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:6">
+      <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>98706.29858659253</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>33.4530708087702</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>0.0003389152595912881</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>0.9996610847404087</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>76.77904902851752</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:6">
+      <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>98672.84551578376</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>33.78771443468255</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>0.0003424216080732956</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>0.9996575783919267</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>75.80490992687348</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:6">
+      <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>98639.05780134907</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>34.1531339818882</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>0.0003462435139097719</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>0.9996537564860902</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>74.83070478794426</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:6">
+      <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>98604.90466736718</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>34.55208297972841</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>0.0003504093746278247</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>0.9996495906253722</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>73.85645022655257</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:6">
+      <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>98570.35258438745</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>34.98756074896936</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>0.0003549501430363255</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>0.9996450498569637</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>72.88216402475733</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:6">
+      <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>98535.36502363849</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>35.46283423144114</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>0.0003598995571075791</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>0.9996401004428924</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>71.90786520686946</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:6">
+      <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>98499.90218940705</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>35.98146173777501</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>0.0003652943905323447</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>0.9996347056094677</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>70.93357411855733</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:6">
+      <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>98463.92072766928</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>36.54731877752113</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>0.0003711747258023923</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>0.9996288252741976</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>69.95931251017805</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:6">
+      <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>98427.37340889176</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>37.16462614973894</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>0.0003775842518457528</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>0.9996224157481542</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>68.98510362446321</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:6">
+      <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>98390.20878274202</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>37.83798048646668</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>0.0003845705884212292</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>0.9996154294115788</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>68.01097228867805</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:6">
+      <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>98352.37080225555</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>38.57238745631022</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>0.0003921856396716938</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>0.9996078143603283</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>67.03694501136124</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:6">
+      <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>98313.79841479924</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>39.37329785228558</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>0.000400485979456966</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>0.999599514020543</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>66.06305008373684</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:6">
+      <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>98274.42511694695</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>40.24664680490676</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>0.0004095332713166533</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>0.9995904667286833</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>65.08931768587217</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:6">
+      <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>98234.17847014204</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>41.19889638012127</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>0.0004193947261710296</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>0.999580605273829</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>64.1157799976333</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:6">
+      <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>98192.97957376191</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>42.23708184114783</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>0.0004301436011463489</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>0.9995698563988537</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>63.14247131446308</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:6">
+      <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>98150.74249192077</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>43.36886187338192</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>0.0004418597432103155</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>0.9995581402567897</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>62.16942816797703</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:6">
+      <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>98107.37363004738</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>44.60257309342774</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>0.0004546301816377163</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>0.9995453698183623</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>61.19668945133493</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:6">
+      <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>98062.77105695395</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>45.94728918522869</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>0.0004685497736806044</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>0.9995314502263194</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>60.22429654930496</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:6">
+      <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>98016.82376776871</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>47.41288502967186</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>0.0004837219082104438</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>0.9995162780917896</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>59.2522934728886</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:6">
+      <c r="A63">
         <v>61</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>97969.41088273904</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>49.01010621771204</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>0.0005002592725230626</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>0.9994997407274769</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>58.28072699831821</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:6">
+      <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>97920.40077652133</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>50.75064436144295</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>0.0005182846879606684</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>0.9994817153120393</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>57.30964681017628</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:6">
+      <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>97869.65013215989</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>52.64721864196064</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>0.0005379320205075588</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>0.9994620679794924</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>56.33910564831118</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:6">
+      <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>97817.00291351794</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>54.71366405712225</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>0.0005593471730624966</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>0.9994406528269375</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>55.36915945814255</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:6">
+      <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>97762.28924946081</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>56.96502685631424</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>0.0005826891666883549</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>0.9994173108333116</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>54.39986754385472</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:6">
+      <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>97705.3242226045</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>59.41766767169015</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>0.0006081313187837889</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>0.9993918686812162</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>53.43129272387042</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:6">
+      <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>97645.90655493281</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>62.0893728764099</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>0.0006358625268277907</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>0.9993641374731722</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>52.46350148787764</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:6">
+      <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>97583.8171820564</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>64.99947471843606</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>0.0006660886671113753</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>0.9993339113328886</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>51.49656415454732</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:6">
+      <c r="A71">
         <v>69</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>97518.81770733796</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>68.16898079278893</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>0.0006990341187007587</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>0.9993009658812992</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>50.53055502892848</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:6">
+      <c r="A72">
         <v>70</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>97450.64872654517</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>71.62071342491795</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>0.0007349434237825525</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>0.9992650565762174</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>49.56555255833837</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:6">
+      <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>97379.02801312026</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>75.37945954008725</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>0.0007740830965157208</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>0.9992259169034843</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>48.60163948537508</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:6">
+      <c r="A74">
         <v>72</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>97303.64855358018</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>79.47213158876346</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>0.000816743593586855</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>0.9991832564064131</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>47.63890299646946</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:6">
+      <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>97224.17642199142</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>83.92794008091059</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>0.0008632414608135131</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>0.9991367585391865</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>46.67743486415662</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:6">
+      <c r="A76">
         <v>74</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>97140.2484819105</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>88.77857825241371</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>0.0009139216713960341</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>0.999086078328604</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>45.71733158098549</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:6">
+      <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>97051.46990365809</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>94.05841934004103</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>0.0009691601727764843</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>0.9990308398272235</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>44.75869448269233</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:6">
+      <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>96957.41148431804</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>99.80472687356804</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>0.001029366660533326</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>0.9989706333394667</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>43.80162985793974</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:6">
+      <c r="A79">
         <v>77</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>96857.60675744448</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>106.0578783009382</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>0.001094987599337793</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>0.9989050124006622</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>42.8462490415623</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:6">
+      <c r="A80">
         <v>78</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>96751.54887914353</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>112.8616021377554</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>0.00116650951271835</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>0.9988334904872816</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>41.89266848785934</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:6">
+      <c r="A81">
         <v>79</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>96638.68727700578</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>120.2632286711688</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>0.001244462565250348</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>0.9987555374347497</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>40.94100982003106</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:6">
+      <c r="A82">
         <v>80</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>96518.42404833461</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>128.3139540409784</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>0.001329424462802264</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>0.9986705755371977</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>39.99139985136067</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:6">
+      <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>96390.11009429363</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>137.0691172596829</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>0.001422024698650048</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>0.99857797530135</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>39.043970573197</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:6">
+      <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>96253.04097703395</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>146.5884894068292</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>0.001522949175619348</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84">
         <v>0.9984770508243807</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>38.09885910418286</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:6">
+      <c r="A85">
         <v>83</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>96106.45248762712</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>156.936573829876</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>0.001632945236950456</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>0.9983670547630495</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>37.15620759449585</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:6">
+      <c r="A86">
         <v>84</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>95949.51591379724</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>168.1829156891081</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>0.001752827141308422</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>0.9982471728586916</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>36.21616307811336</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:6">
+      <c r="A87">
         <v>85</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>95781.33299810813</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>180.4024185814082</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>0.00188348202029065</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>0.9981165179797094</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>35.27887726526946</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:6">
+      <c r="A88">
         <v>86</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>95600.93057952673</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>193.6756652490951</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>0.002025876359937562</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88">
         <v>0.9979741236400624</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>34.34450626632799</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:6">
+      <c r="A89">
         <v>87</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>95407.25491427763</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>208.0892385026127</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>0.002181063051123089</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>0.9978189369488769</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>33.41321023723721</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:6">
+      <c r="A90">
         <v>88</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>95199.16567577502</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>223.7360374372093</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>0.002350189057320096</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>0.9976498109426799</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>32.48515293554055</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:6">
+      <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>94975.42963833781</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>240.7155827744497</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>0.002534503752087081</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>0.9974654962479129</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>31.56050117457324</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:6">
+      <c r="A92">
         <v>90</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>94734.71405556337</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>259.1343036817423</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>0.002735367982741321</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>0.9972646320172587</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>30.63942416194953</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:6">
+      <c r="A93">
         <v>91</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>94475.57975188163</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>279.1057966810795</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>0.002954263921048028</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>0.997045736078952</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>29.72209270671091</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:6">
+      <c r="A94">
         <v>92</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>94196.47395520055</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>300.7510452177306</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>0.003192805766389584</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>0.9968071942336104</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>28.8086782775198</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:6">
+      <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>93895.72290998281</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>324.198586080553</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>0.003452751371767593</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95">
         <v>0.9965472486282324</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>27.89935189200231</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:6">
+      <c r="A96">
         <v>94</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>93571.52432390225</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>349.5846061085199</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>0.003736014868138904</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96">
         <v>0.9962639851318611</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>26.99428281470656</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:6">
+      <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>93221.93971779374</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>377.0529494411927</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>0.004044680367975895</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97">
         <v>0.9959553196320241</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>26.09363703807871</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:6">
+      <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>92844.88676835255</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98">
         <v>406.7550119344688</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>0.004381016834554607</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98">
         <v>0.9956189831654454</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>25.19757551727801</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:6">
+      <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>92438.13175641808</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99">
         <v>438.8494952313445</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>0.004747494209291769</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99">
         <v>0.9952525057907082</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>24.30625212544177</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:6">
+      <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>91999.28226118673</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100">
         <v>473.5019883200846</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>0.005146800895422299</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100">
         <v>0.9948531991045777</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>23.41981129103331</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:6">
+      <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>91525.78027286664</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101">
         <v>510.8843392123812</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>0.00558186270239136</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101">
         <v>0.9944181372976086</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>22.53838527298539</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
+    <row r="102" spans="1:6">
+      <c r="A102">
         <v>100</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102">
         <v>91014.89593365426</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>551.1737736317946</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>0.006055863361460911</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102">
         <v>0.9939441366385391</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>21.6620910222696</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:6">
+      <c r="A103">
         <v>101</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>90463.72216002247</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>594.551711342917</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>0.006572266729100606</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103">
         <v>0.9934277332708994</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>20.79102657000277</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:6">
+      <c r="A104">
         <v>102</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>89869.17044867955</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104">
         <v>641.2022240383039</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>0.007134840800655518</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104">
         <v>0.9928651591993445</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>19.92526687189795</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:6">
+      <c r="A105">
         <v>103</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>89227.96822464124</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105">
         <v>691.3100716425827</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>0.00774768366239309</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105">
         <v>0.9922523163376069</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>19.06485902633814</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
+    <row r="106" spans="1:6">
+      <c r="A106">
         <v>104</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>88536.65815299866</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106">
         <v>745.0582466708354</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>0.00841525151517819</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106">
         <v>0.9915847484848218</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>18.20981676803824</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
+    <row r="107" spans="1:6">
+      <c r="A107">
         <v>105</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107">
         <v>87791.59990632783</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107">
         <v>802.6249491525476</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107">
         <v>0.009142388907468768</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107">
         <v>0.9908576110925312</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>17.36011412045162</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:6">
+      <c r="A108">
         <v>106</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>86988.97495717528</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>864.179907978371</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108">
         <v>0.009934361318820084</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108">
         <v>0.9900656386811799</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108">
         <v>16.51567806686317</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:6">
+      <c r="A109">
         <v>107</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109">
         <v>86124.79504919691</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109">
         <v>929.879958855374</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109">
         <v>0.01079689023729113</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109">
         <v>0.9892031097627089</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>15.67638007132225</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:6">
+      <c r="A110">
         <v>108</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110">
         <v>85194.91509034153</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110">
         <v>999.8637850525954</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110">
         <v>0.01173619087468225</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110">
         <v>0.9882638091253177</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>14.84202624470396</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:6">
+      <c r="A111">
         <v>109</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111">
         <v>84195.05130528893</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111">
         <v>1074.245725675057</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111">
         <v>0.01275901266191848</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111">
         <v>0.9872409873380815</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>14.0123459062997</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:6">
+      <c r="A112">
         <v>110</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112">
         <v>83120.80557961387</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112">
         <v>1153.108558462517</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112">
         <v>0.01387268266256225</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112">
         <v>0.9861273173374377</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>13.18697823490222</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:6">
+      <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113">
         <v>81967.69702115135</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113">
         <v>1236.495171498737</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113">
         <v>0.0150851520347054</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113">
         <v>0.9849148479652946</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>12.36545663206786</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:6">
+      <c r="A114">
         <v>112</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114">
         <v>80731.20184965261</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114">
         <v>1324.399052494627</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114">
         <v>0.01640504565955903</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114">
         <v>0.983594954340441</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>11.54719032978368</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="n">
+    <row r="115" spans="1:6">
+      <c r="A115">
         <v>113</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115">
         <v>79406.80279715799</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115">
         <v>1416.75354758196</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115">
         <v>0.01784171503795473</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115">
         <v>0.9821582849620453</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115">
         <v>10.73144265943442</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="n">
+    <row r="116" spans="1:6">
+      <c r="A116">
         <v>114</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116">
         <v>77990.04924957603</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116">
         <v>1513.419876297828</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116">
         <v>0.01940529453257211</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116">
         <v>0.9805947054674279</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116">
         <v>9.917305251189534</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="n">
+    <row r="117" spans="1:6">
+      <c r="A117">
         <v>115</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117">
         <v>76476.62937327819</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117">
         <v>1614.173938472536</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117">
         <v>0.02110676100268283</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117">
         <v>0.9788932389973172</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117">
         <v>9.103667242625498</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="n">
+    <row r="118" spans="1:6">
+      <c r="A118">
         <v>116</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118">
         <v>74862.45543480566</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118">
         <v>1718.692015156838</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118">
         <v>0.02295799683799538</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118">
         <v>0.9770420031620046</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118">
         <v>8.289178329026214</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="n">
+    <row r="119" spans="1:6">
+      <c r="A119">
         <v>117</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119">
         <v>73143.76341964882</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119">
         <v>1826.535552792974</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119">
         <v>0.02497185634698018</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119">
         <v>0.9750281436530198</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119">
         <v>7.472204167086028</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="n">
+    <row r="120" spans="1:6">
+      <c r="A120">
         <v>118</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120">
         <v>71317.22786685584</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120">
         <v>1937.135330736752</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120">
         <v>0.02716223539077045</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120">
         <v>0.9728377646092295</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120">
         <v>6.650772223829473</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="n">
+    <row r="121" spans="1:6">
+      <c r="A121">
         <v>119</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121">
         <v>69380.09253611909</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121">
         <v>2049.775449749399</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121">
         <v>0.02954414407392569</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121">
         <v>0.9704558559260743</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121">
         <v>5.822505609452899</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="n">
+    <row r="122" spans="1:6">
+      <c r="A122">
         <v>120</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122">
         <v>67330.31708636969</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122">
         <v>2163.577745065186</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122">
         <v>0.03213378220527019</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122">
         <v>0.9678662177947298</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122">
         <v>4.984541699605498</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="n">
+    <row r="123" spans="1:6">
+      <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123">
         <v>65166.7393413045</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123">
         <v>2277.487422360631</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123">
         <v>0.0349486171224942</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123">
         <v>0.9650513828775058</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123">
         <v>4.133431374248671</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="n">
+    <row r="124" spans="1:6">
+      <c r="A124">
         <v>122</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124">
         <v>62889.25191894387</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124">
         <v>2390.26093614141</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124">
         <v>0.03800746332969818</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124">
         <v>0.9619925366703018</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124">
         <v>3.265013385520285</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="n">
+    <row r="125" spans="1:6">
+      <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125">
         <v>60498.99098280246</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125">
         <v>2500.457371775463</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125">
         <v>0.04133056322354611</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125">
         <v>0.9586694367764539</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125">
         <v>2.374256587364691</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="n">
+    <row r="126" spans="1:6">
+      <c r="A126">
         <v>124</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126">
         <v>57998.533611027</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126">
         <v>2606.434843619421</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126">
         <v>0.04493966797677573</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126">
         <v>0.9550603320232243</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126">
         <v>1.455060332023224</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="n">
+    <row r="127" spans="1:6">
+      <c r="A127">
         <v>125</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127">
         <v>55392.09876740758</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127">
         <v>55392.09876740758</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127">
         <v>1</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127">
         <v>0</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>